--- a/evaluation_surveys/009_institutional_innovation_readiness_survey--evaluation_surveys.xlsx
+++ b/evaluation_surveys/009_institutional_innovation_readiness_survey--evaluation_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Innovation Capabilities</t>
+          <t>Page4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Innovation Readiness</t>
+          <t>Page6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Innovation Readiness</t>
+          <t>Page7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Innovation Readiness</t>
+          <t>Page8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Readiness Score</t>
+          <t>Page10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Readiness Score</t>
+          <t>Page11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Page25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
